--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -590,27 +590,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -633,7 +633,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -712,27 +712,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -755,7 +755,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -834,27 +834,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -877,7 +877,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -956,27 +956,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -999,7 +999,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1078,27 +1078,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1200,27 +1200,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1322,27 +1322,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1444,27 +1444,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1566,27 +1566,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1688,27 +1688,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>£49.32</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1810,27 +1810,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1932,27 +1932,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2054,27 +2054,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2175,27 +2175,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2297,27 +2297,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2517,27 +2517,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2638,27 +2638,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2759,27 +2759,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2880,27 +2880,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3001,27 +3001,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£43.70</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£43.70</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3122,27 +3122,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3243,27 +3243,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>£924.50</t>
+          <t>£925.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£924.50</t>
+          <t>£925.00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3364,27 +3364,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£44.65</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£44.65</t>
+          <t>£42.90</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3485,27 +3485,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7b167e995+80021]
-	GetHandleVerifier [0x0x7ff7b167e9f0+80112]
-	(No symbol) [0x0x7ff7b140060f]
-	(No symbol) [0x0x7ff7b1458854]
-	(No symbol) [0x0x7ff7b1458b1c]
-	(No symbol) [0x0x7ff7b14ac927]
-	(No symbol) [0x0x7ff7b148126f]
-	(No symbol) [0x0x7ff7b14a968a]
-	(No symbol) [0x0x7ff7b1481003]
-	(No symbol) [0x0x7ff7b14495d1]
-	(No symbol) [0x0x7ff7b144a3f3]
-	GetHandleVerifier [0x0x7ff7b193dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7b193800a+2936586]
-	GetHandleVerifier [0x0x7ff7b1958a47+3070279]
-	GetHandleVerifier [0x0x7ff7b169847e+185214]
-	GetHandleVerifier [0x0x7ff7b169fecf+216527]
-	GetHandleVerifier [0x0x7ff7b1687bd4+117460]
-	GetHandleVerifier [0x0x7ff7b1687d8f+117903]
-	GetHandleVerifier [0x0x7ff7b166dc68+11112]
+	GetHandleVerifier [0x0x7ff7eac8e995+80021]
+	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
+	(No symbol) [0x0x7ff7eaa1060f]
+	(No symbol) [0x0x7ff7eaa68854]
+	(No symbol) [0x0x7ff7eaa68b1c]
+	(No symbol) [0x0x7ff7eaabc927]
+	(No symbol) [0x0x7ff7eaa9126f]
+	(No symbol) [0x0x7ff7eaab968a]
+	(No symbol) [0x0x7ff7eaa91003]
+	(No symbol) [0x0x7ff7eaa595d1]
+	(No symbol) [0x0x7ff7eaa5a3f3]
+	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
+	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
+	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
+	GetHandleVerifier [0x0x7ff7eaca847e+185214]
+	GetHandleVerifier [0x0x7ff7eacafecf+216527]
+	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
+	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
+	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,163.00</t>
+          <t>£1,150.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,268.00</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,268.00</t>
+          <t>£1,250.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,210.00</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,210.00</t>
+          <t>£1,225.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£49.32</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>£34.64</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£43.60</t>
+          <t>£39.10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£48.65</t>
+          <t>£43.59</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£43.80</t>
+          <t>£43.85</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.81</t>
+          <t>£43.85</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7eac8e995+80021]
-	GetHandleVerifier [0x0x7ff7eac8e9f0+80112]
-	(No symbol) [0x0x7ff7eaa1060f]
-	(No symbol) [0x0x7ff7eaa68854]
-	(No symbol) [0x0x7ff7eaa68b1c]
-	(No symbol) [0x0x7ff7eaabc927]
-	(No symbol) [0x0x7ff7eaa9126f]
-	(No symbol) [0x0x7ff7eaab968a]
-	(No symbol) [0x0x7ff7eaa91003]
-	(No symbol) [0x0x7ff7eaa595d1]
-	(No symbol) [0x0x7ff7eaa5a3f3]
-	GetHandleVerifier [0x0x7ff7eaf4dd4d+2960461]
-	GetHandleVerifier [0x0x7ff7eaf4800a+2936586]
-	GetHandleVerifier [0x0x7ff7eaf68a47+3070279]
-	GetHandleVerifier [0x0x7ff7eaca847e+185214]
-	GetHandleVerifier [0x0x7ff7eacafecf+216527]
-	GetHandleVerifier [0x0x7ff7eac97bd4+117460]
-	GetHandleVerifier [0x0x7ff7eac97d8f+117903]
-	GetHandleVerifier [0x0x7ff7eac7dc68+11112]
+	GetHandleVerifier [0x0x7ff62672e995+80021]
+	GetHandleVerifier [0x0x7ff62672e9f0+80112]
+	(No symbol) [0x0x7ff6264b060f]
+	(No symbol) [0x0x7ff626508854]
+	(No symbol) [0x0x7ff626508b1c]
+	(No symbol) [0x0x7ff62655c927]
+	(No symbol) [0x0x7ff62653126f]
+	(No symbol) [0x0x7ff62655968a]
+	(No symbol) [0x0x7ff626531003]
+	(No symbol) [0x0x7ff6264f95d1]
+	(No symbol) [0x0x7ff6264fa3f3]
+	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
+	GetHandleVerifier [0x0x7ff6269e800a+2936586]
+	GetHandleVerifier [0x0x7ff626a08a47+3070279]
+	GetHandleVerifier [0x0x7ff62674847e+185214]
+	GetHandleVerifier [0x0x7ff62674fecf+216527]
+	GetHandleVerifier [0x0x7ff626737bd4+117460]
+	GetHandleVerifier [0x0x7ff626737d8f+117903]
+	GetHandleVerifier [0x0x7ff62671dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,163.00</t>
+          <t>£1,150.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_09-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£10.50</t>
+          <t>£9.99</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -590,27 +590,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -633,7 +633,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>£10.95 Pre Sale Price-£11.99</t>
+          <t>£10.04 Pre Sale Price-£11.99</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£12.25</t>
+          <t>£11.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -712,27 +712,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -755,7 +755,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>£12.30 Pre Sale Price-£13.99</t>
+          <t>£11.33 Pre Sale Price-£13.99</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£15.38</t>
+          <t>£14.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -834,27 +834,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -877,7 +877,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>£15.75 Pre Sale Price-£17.99</t>
+          <t>£14.65 Pre Sale Price-£17.99</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£15.65</t>
+          <t>£14.90</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -956,27 +956,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -999,7 +999,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>£16.50 Pre Sale Price-£19.99</t>
+          <t>£14.94 Pre Sale Price-£19.99</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£19.99</t>
+          <t>£18.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1078,27 +1078,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>£20.59 Pre Sale Price-£21.99</t>
+          <t>£19.01 Pre Sale Price-£21.99</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£21.99</t>
+          <t>£20.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1200,27 +1200,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>£22.76 Pre Sale Price-£24.99</t>
+          <t>£20.73 Pre Sale Price-£24.99</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£22.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1322,27 +1322,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>£23.50 Pre Sale Price-£25.99</t>
+          <t>£20.93 Pre Sale Price-£25.99</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£25.26</t>
+          <t>£23.98</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£26.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1444,27 +1444,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>£25.79 Pre Sale Price-£27.99</t>
+          <t>£24.03 Pre Sale Price-£27.99</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£27.33</t>
+          <t>£25.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1566,27 +1566,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>£28.80 Pre Sale Price-£31.99</t>
+          <t>£26.04 Pre Sale Price-£31.99</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£26.99</t>
+          <t>£25.70</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1688,27 +1688,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>£27.38 Pre Sale Price-£32.99</t>
+          <t>£25.71 Pre Sale Price-£32.99</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£35.56</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1810,27 +1810,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>£36.30 Pre Sale Price-£39.99</t>
+          <t>£34.99 Pre Sale Price-£39.99</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£33.70</t>
+          <t>£31.39</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1932,27 +1932,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>£34.90 Pre Sale Price-£37.99</t>
+          <t>£31.43 Pre Sale Price-£37.99</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£40.25</t>
+          <t>£39.69</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2054,27 +2054,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>£41.09 Pre Sale Price-£44.99</t>
+          <t>£38.56 Pre Sale Price-£44.99</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£41.05</t>
+          <t>£38.99</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2175,27 +2175,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£38.29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2297,27 +2297,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>£43.50 Pre Sale Price-£49.99</t>
+          <t>£38.32 Pre Sale Price-£49.99</t>
         </is>
       </c>
     </row>
@@ -2517,27 +2517,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>£962.37 Pre Sale Price-£1,040.00</t>
+          <t>£958.33 Pre Sale Price-£1,040.00</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£29.50</t>
+          <t>£28.94</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2638,27 +2638,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£35.90</t>
+          <t>£34.59</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find'</t>
+          <t>£34.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2759,27 +2759,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£39.15</t>
+          <t>£39.09</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2880,27 +2880,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£43.62</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3001,27 +3001,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3122,27 +3122,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3243,27 +3243,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3364,27 +3364,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3485,27 +3485,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff62672e995+80021]
-	GetHandleVerifier [0x0x7ff62672e9f0+80112]
-	(No symbol) [0x0x7ff6264b060f]
-	(No symbol) [0x0x7ff626508854]
-	(No symbol) [0x0x7ff626508b1c]
-	(No symbol) [0x0x7ff62655c927]
-	(No symbol) [0x0x7ff62653126f]
-	(No symbol) [0x0x7ff62655968a]
-	(No symbol) [0x0x7ff626531003]
-	(No symbol) [0x0x7ff6264f95d1]
-	(No symbol) [0x0x7ff6264fa3f3]
-	GetHandleVerifier [0x0x7ff6269edd4d+2960461]
-	GetHandleVerifier [0x0x7ff6269e800a+2936586]
-	GetHandleVerifier [0x0x7ff626a08a47+3070279]
-	GetHandleVerifier [0x0x7ff62674847e+185214]
-	GetHandleVerifier [0x0x7ff62674fecf+216527]
-	GetHandleVerifier [0x0x7ff626737bd4+117460]
-	GetHandleVerifier [0x0x7ff626737d8f+117903]
-	GetHandleVerifier [0x0x7ff62671dc68+11112]
+	GetHandleVerifier [0x0x7ff7aad1e995+80021]
+	GetHandleVerifier [0x0x7ff7aad1e9f0+80112]
+	(No symbol) [0x0x7ff7aaaa060f]
+	(No symbol) [0x0x7ff7aaaf8854]
+	(No symbol) [0x0x7ff7aaaf8b1c]
+	(No symbol) [0x0x7ff7aab4c927]
+	(No symbol) [0x0x7ff7aab2126f]
+	(No symbol) [0x0x7ff7aab4968a]
+	(No symbol) [0x0x7ff7aab21003]
+	(No symbol) [0x0x7ff7aaae95d1]
+	(No symbol) [0x0x7ff7aaaea3f3]
+	GetHandleVerifier [0x0x7ff7aafddd4d+2960461]
+	GetHandleVerifier [0x0x7ff7aafd800a+2936586]
+	GetHandleVerifier [0x0x7ff7aaff8a47+3070279]
+	GetHandleVerifier [0x0x7ff7aad3847e+185214]
+	GetHandleVerifier [0x0x7ff7aad3fecf+216527]
+	GetHandleVerifier [0x0x7ff7aad27bd4+117460]
+	GetHandleVerifier [0x0x7ff7aad27d8f+117903]
+	GetHandleVerifier [0x0x7ff7aad0dc68+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1255.2</t>
+          <t>£1229.44</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
